--- a/filelist.xlsx
+++ b/filelist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Desktop/revised_version_20251208/Local dependence toolbox 20251208/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Desktop/revised_version_20260306/local dependence toolbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1581D6E9-04A1-3842-B2D5-1A2CCA77D1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6C9247-D96E-1B41-8872-0F2A93DF56A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="500" windowWidth="17680" windowHeight="15620" xr2:uid="{772B97B5-03B2-AC48-B62B-9B7792D58D6B}"/>
+    <workbookView xWindow="7120" yWindow="500" windowWidth="19140" windowHeight="15620" xr2:uid="{772B97B5-03B2-AC48-B62B-9B7792D58D6B}"/>
   </bookViews>
   <sheets>
     <sheet name="file list" sheetId="1" r:id="rId1"/>
@@ -178,18 +178,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Function for estimating clayton, gumbel and frank copula models</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Generate data from the FGM copula model</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Draw quantile kendall's tau curves</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Draw quantile Kendall's tau curve along the main diagonal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -222,10 +214,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>copula mis-spec/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>scenario_1.m</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -254,10 +242,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Reproduce simulation results in Section 5: comparative analysis of global and local kendall's tau for copula models</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Reproduce results in Web Figures 7, 9, 11, and 13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -270,10 +254,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Results for the copula model misspecification experiments (Web Tables 6,7, and 8)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Characterize the marginal distribution features of CSF FAM171A2 and total α-syn, and draw their scatter plot </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -283,6 +263,26 @@
   </si>
   <si>
     <t>Folder containing all core functions used in this package. Readers can refer to each file for a more detailed introduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copula_misspec/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function for estimating Clayton, Gumbel and Frank copula models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw quantile Kendall's tau curves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reproduce simulation results in Section 5: comparative analysis of global and local Kendall's tau for copula models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Results for the copula model misspecification experiments (Web Tables 6, 7, and 8)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -411,9 +411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -451,7 +451,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -557,7 +557,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -699,7 +699,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>26</v>
@@ -778,7 +778,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -814,7 +814,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -836,7 +836,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1">
@@ -844,7 +844,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="5"/>
       <c r="E10" s="7" t="s">
@@ -882,11 +882,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5"/>
       <c r="E13" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -920,11 +920,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5"/>
       <c r="E16" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -950,7 +950,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -961,7 +961,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -972,7 +972,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -980,13 +980,13 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -994,10 +994,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="7" customFormat="1">
@@ -1005,11 +1005,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="5"/>
       <c r="E23" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -1024,7 +1024,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1035,7 +1035,7 @@
         <v>15</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1046,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="7" customFormat="1">
@@ -1054,11 +1054,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="5"/>
       <c r="E27" s="7" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -1073,7 +1073,7 @@
         <v>16</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="7" customFormat="1">
@@ -1097,7 +1097,7 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>

--- a/filelist.xlsx
+++ b/filelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Desktop/revised_version_20260306/local dependence toolbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6C9247-D96E-1B41-8872-0F2A93DF56A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9608F023-E46B-BC4A-8E98-362F3537E281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="500" windowWidth="19140" windowHeight="15620" xr2:uid="{772B97B5-03B2-AC48-B62B-9B7792D58D6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>/</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -283,6 +283,10 @@
   </si>
   <si>
     <t>Results for the copula model misspecification experiments (Web Tables 6, 7, and 8)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5E5241-435D-1646-9C1E-010F994308C5}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
@@ -1104,6 +1108,11 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
+    <row r="31" spans="1:9">
+      <c r="C31" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/filelist.xlsx
+++ b/filelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Desktop/revised_version_20260306/local dependence toolbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9608F023-E46B-BC4A-8E98-362F3537E281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C628E5D9-85A2-6446-AAEB-9D9E428DF710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="500" windowWidth="19140" windowHeight="15620" xr2:uid="{772B97B5-03B2-AC48-B62B-9B7792D58D6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>/</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -283,10 +283,6 @@
   </si>
   <si>
     <t>Results for the copula model misspecification experiments (Web Tables 6, 7, and 8)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1109,8 +1105,8 @@
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="C31" s="1" t="s">
-        <v>62</v>
+      <c r="C31" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
